--- a/output/pdf_financials_xlsx/NIC.xlsx
+++ b/output/pdf_financials_xlsx/NIC.xlsx
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.507005</v>
+        <v>0.606403</v>
       </c>
     </row>
     <row r="93">
@@ -3478,7 +3478,11 @@
           <t>Warrant reserve 99,398</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NIC.xlsx
+++ b/output/pdf_financials_xlsx/NIC.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2.46604</v>
+        <v>14.335286</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3.127789</v>
+        <v>17.405491</v>
       </c>
     </row>
     <row r="11">
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.753355</v>
       </c>
     </row>
     <row r="35">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.753355</v>
       </c>
     </row>
     <row r="37">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.003657</v>
+        <v>0.250302</v>
       </c>
     </row>
     <row r="49">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-1.793657</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-2.100976</v>
       </c>
     </row>
     <row r="125">
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-1.793657</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-2.100976</v>
       </c>
     </row>
     <row r="126">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4376,7 +4376,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="n">
         <v>-1.793657</v>
       </c>
@@ -5214,7 +5218,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">

--- a/output/pdf_financials_xlsx/NIC.xlsx
+++ b/output/pdf_financials_xlsx/NIC.xlsx
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.274339</v>
+        <v>1.245055</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.252823</v>
+        <v>1.234872</v>
       </c>
     </row>
     <row r="29">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.718237</v>
+        <v>-0.747521</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.951699</v>
+        <v>1.933748</v>
       </c>
     </row>
     <row r="30">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-5.043302431957096</v>
+        <v>-2.194094573239314</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2.043819299898058</v>
+        <v>4.152816682101452</v>
       </c>
     </row>
     <row r="31">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.245055</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.234872</v>
       </c>
     </row>
     <row r="101">
@@ -3834,7 +3834,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
         <v>1.245055</v>
       </c>
@@ -5116,7 +5120,11 @@
           <t>Depreciation of right-of-use assets 8</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
         <v>1.245055</v>
       </c>

--- a/output/pdf_financials_xlsx/NIC.xlsx
+++ b/output/pdf_financials_xlsx/NIC.xlsx
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-1.992576</v>
+        <v>-4.048929</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.6988760000000001</v>
+        <v>1.323347</v>
       </c>
     </row>
     <row r="17">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>2.056353</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.624471</v>
       </c>
     </row>
     <row r="18">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.992576</v>
+        <v>-4.048929</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.6988760000000001</v>
+        <v>1.323347</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.747521</v>
+        <v>-2.803874</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.933748</v>
+        <v>2.558219</v>
       </c>
     </row>
     <row r="30">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-2.194094573239314</v>
+        <v>-8.229821941386007</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4.152816682101452</v>
+        <v>5.493898139607071</v>
       </c>
     </row>
     <row r="31">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-50.78757864116659</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>47.18875699268597</v>
       </c>
     </row>
     <row r="32">
@@ -1318,10 +1318,8 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>3.738452</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>4.630018</v>
@@ -1414,7 +1412,7 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>1.059713</v>
       </c>
     </row>
     <row r="71">
@@ -1429,7 +1427,7 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0.5453789999999999</v>
+        <v>1.605092</v>
       </c>
     </row>
     <row r="72">
@@ -1489,7 +1487,7 @@
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1.610262</v>
+        <v>0.550549</v>
       </c>
     </row>
     <row r="76">
@@ -1564,7 +1562,7 @@
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>12.17163460788037</v>
+        <v>14.92844655799458</v>
       </c>
     </row>
     <row r="81">
@@ -1981,10 +1979,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.220475</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="111">
@@ -2059,10 +2057,10 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.101838</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.150608</v>
       </c>
     </row>
     <row r="117">
@@ -3056,7 +3054,11 @@
           <t>Lease liabilities 10 1,260,114</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -3730,7 +3732,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>0.220475</v>
       </c>
@@ -3782,7 +3788,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>-0.063777</v>
       </c>
@@ -4436,7 +4446,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E77" s="5" t="n">
         <v>-0.101838</v>
       </c>
@@ -5404,7 +5418,11 @@
           <t>Income (loss) before income tax recovery</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="n">
         <v>-2.056353</v>
       </c>
